--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B21D3B-419E-48E2-8D82-42805527C91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82500FF-A812-49EF-9A8F-D41E0F758BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="93">
   <si>
     <t>Client</t>
   </si>
@@ -83,9 +83,6 @@
     <t>LegalEntity</t>
   </si>
   <si>
-    <t>HL Consulting, Inc.</t>
-  </si>
-  <si>
     <t>DisclosureStatus</t>
   </si>
   <si>
@@ -101,15 +98,6 @@
     <t>CaoUser</t>
   </si>
   <si>
-    <t>Retainer</t>
-  </si>
-  <si>
-    <t>MonthlyFee</t>
-  </si>
-  <si>
-    <t>ContingentFee</t>
-  </si>
-  <si>
     <t>ClientOwnership</t>
   </si>
   <si>
@@ -119,30 +107,9 @@
     <t>Public Equity</t>
   </si>
   <si>
-    <t>SICCode</t>
-  </si>
-  <si>
-    <t>OpportunityDescription</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
-    <t>ReferralContact</t>
-  </si>
-  <si>
-    <t>Agreement</t>
-  </si>
-  <si>
-    <t>Yes, separate signed agreement</t>
-  </si>
-  <si>
-    <t>Outcome</t>
-  </si>
-  <si>
-    <t>Cleared</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -158,27 +125,12 @@
     <t>Party</t>
   </si>
   <si>
-    <t>RecordType</t>
-  </si>
-  <si>
-    <t>FASJobType</t>
-  </si>
-  <si>
-    <t>Consulting</t>
-  </si>
-  <si>
     <t>ClientType</t>
   </si>
   <si>
     <t>External</t>
   </si>
   <si>
-    <t>MarketCap</t>
-  </si>
-  <si>
-    <t>Fee</t>
-  </si>
-  <si>
     <t>Contact2</t>
   </si>
   <si>
@@ -326,12 +278,6 @@
     <t>Opportunity Detail - SIC Code., Opportunity Description - Opportunity Description., Estimated Financials - Est. Transaction Size/Market Cap., Estimated Fees - Retainer, input zero if there's no Retainer fee., Estimated Fees - Tail Expires., Estimated Fees - Progress/Monthly Fee., Estimated Fees - Contingent Fee., Referral Information - Referral Contact name is required., HL Internal Team - Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional)., Legal Matters - Confidentiality Agreement, Conflicts Check - A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed., Administration - Estimated Closed Date., Administration - "Women Led" is required. Please update this field with the correct value, Administration - Fairness Opinion Component., Administration - Date Engaged - Date of Executed Retainer or similar document., Approved NBC form - Please complete and submit this form via the NBC button., Opportunity Contacts - Add at least one Primary Opportunity Contact., Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>9999</t>
-  </si>
-  <si>
     <t>Estimated Financials - Client/Subject: EBITDA(MM), please provide a EBITDA(MM) value on the Client or Subject Company record in Company Financials</t>
   </si>
   <si>
@@ -350,26 +296,26 @@
     <t>Opportunities</t>
   </si>
   <si>
-    <t>FVA</t>
-  </si>
-  <si>
-    <t>Drew Koecher</t>
-  </si>
-  <si>
     <t>Dimitri Drone</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
     <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: SIC Code is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: \"Women Led\" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Approved FEIS form - Please complete and submit this form via the FEIS button.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Opportunity Contacts - Add at least one Contact with an approrpriate Role - confirm with FVA BUAs.Info--&gt;Administration--&gt;Service &amp; Transaction Type: Transaction Type is required.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
+  </si>
+  <si>
+    <t>Activism Advisory</t>
+  </si>
+  <si>
+    <t>HL Capital, Inc.</t>
+  </si>
+  <si>
+    <t>Rob Oudman</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,6 +333,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -412,14 +365,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -438,6 +389,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,11 +670,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -733,17 +684,11 @@
     <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -781,63 +726,27 @@
         <v>16</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -864,55 +773,19 @@
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>107</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="R2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S2" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="U2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V2" t="s">
-        <v>95</v>
-      </c>
-      <c r="W2" t="s">
-        <v>34</v>
-      </c>
-      <c r="X2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -932,15 +805,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -958,12 +831,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -978,12 +851,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1008,76 +881,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="F2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>100</v>
+      <c r="H2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1091,318 +964,318 @@
   <dimension ref="A1:AF33"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="95.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="8" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="8"/>
-    <col min="8" max="8" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.88671875" style="8"/>
-    <col min="13" max="13" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="3"/>
-    <col min="15" max="16" width="8.88671875" style="8"/>
-    <col min="17" max="17" width="10.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.88671875" style="8"/>
-    <col min="21" max="21" width="9.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.88671875" style="8"/>
-    <col min="23" max="23" width="13.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.88671875" style="8"/>
-    <col min="31" max="31" width="10.5546875" style="8" customWidth="1"/>
-    <col min="32" max="32" width="102.33203125" style="8" customWidth="1"/>
-    <col min="33" max="16384" width="8.88671875" style="8"/>
+    <col min="1" max="1" width="95.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="6"/>
+    <col min="8" max="8" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.88671875" style="6"/>
+    <col min="13" max="13" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="2"/>
+    <col min="15" max="16" width="8.88671875" style="6"/>
+    <col min="17" max="17" width="10.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.88671875" style="6"/>
+    <col min="21" max="21" width="9.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="6"/>
+    <col min="23" max="23" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.88671875" style="6"/>
+    <col min="31" max="31" width="10.5546875" style="6" customWidth="1"/>
+    <col min="32" max="32" width="102.33203125" style="6" customWidth="1"/>
+    <col min="33" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="P1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="Q1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="R1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="S1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="U1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="216" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" s="9" t="s">
+      <c r="K2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="V1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="W1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="X1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y1" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA1" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB1" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC1" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD1" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE1" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF1" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="216" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF2" s="7" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
+      <c r="A3" s="3"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
+      <c r="A4" s="3"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+      <c r="A5" s="3"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+      <c r="A6" s="3"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
+      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+      <c r="A11" s="3"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
+      <c r="A12" s="3"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
+      <c r="A13" s="3"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+      <c r="A14" s="3"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
+      <c r="A15" s="3"/>
     </row>
     <row r="16" spans="1:32" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
+      <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+      <c r="A17" s="3"/>
     </row>
     <row r="18" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+      <c r="A18" s="3"/>
     </row>
     <row r="19" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
+      <c r="A19" s="3"/>
     </row>
     <row r="20" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
+      <c r="A20" s="3"/>
     </row>
     <row r="21" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
+      <c r="A21" s="3"/>
     </row>
     <row r="22" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
+      <c r="A22" s="3"/>
     </row>
     <row r="23" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
+      <c r="A23" s="3"/>
     </row>
     <row r="24" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
+      <c r="A24" s="3"/>
     </row>
     <row r="25" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
+      <c r="A25" s="3"/>
     </row>
     <row r="26" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
+      <c r="A26" s="3"/>
     </row>
     <row r="27" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
+      <c r="A27" s="3"/>
     </row>
     <row r="28" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
+      <c r="A28" s="3"/>
     </row>
     <row r="29" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
+      <c r="A29" s="3"/>
     </row>
     <row r="30" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
+      <c r="A30" s="3"/>
     </row>
     <row r="31" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
+      <c r="A31" s="3"/>
     </row>
     <row r="32" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
+      <c r="A32" s="3"/>
     </row>
     <row r="33" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
+      <c r="A33" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82500FF-A812-49EF-9A8F-D41E0F758BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F47DA49-A83E-4E9C-863B-A8F920B5E83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
   <si>
     <t>Client</t>
   </si>
@@ -299,23 +299,80 @@
     <t>Dimitri Drone</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: SIC Code is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: \"Women Led\" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Approved FEIS form - Please complete and submit this form via the FEIS button.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Opportunity Contacts - Add at least one Contact with an approrpriate Role - confirm with FVA BUAs.Info--&gt;Administration--&gt;Service &amp; Transaction Type: Transaction Type is required.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
-  </si>
-  <si>
     <t>Activism Advisory</t>
   </si>
   <si>
     <t>HL Capital, Inc.</t>
   </si>
   <si>
-    <t>Rob Oudman</t>
+    <t>Retainer</t>
+  </si>
+  <si>
+    <t>MonthlyFee</t>
+  </si>
+  <si>
+    <t>ContingentFee</t>
+  </si>
+  <si>
+    <t>SICCode</t>
+  </si>
+  <si>
+    <t>OpportunityDescription</t>
+  </si>
+  <si>
+    <t>ReferralContact</t>
+  </si>
+  <si>
+    <t>Agreement</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>RecordType</t>
+  </si>
+  <si>
+    <t>FASJobType</t>
+  </si>
+  <si>
+    <t>MarketCap</t>
+  </si>
+  <si>
+    <t>Fee</t>
+  </si>
+  <si>
+    <t>WomenLed</t>
+  </si>
+  <si>
+    <t>James Craven</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>Yes, separate signed agreement</t>
+  </si>
+  <si>
+    <t>Cleared</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>Consulting</t>
+  </si>
+  <si>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: SIC Code is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Tail Expires is required.Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: \"Women Led\" is required. Please update this field with the correct valueInfo--&gt;Administration: Fairness Opinion Component is required.Info--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,13 +390,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -389,7 +439,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -670,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -688,7 +738,7 @@
     <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -731,22 +781,64 @@
       <c r="N1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="O1" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="R1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T1" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>78</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
-      <c r="C2" t="s">
-        <v>90</v>
+      <c r="C2" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -773,19 +865,61 @@
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M2" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="9" t="s">
-        <v>92</v>
+      <c r="N2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="R2" t="s">
         <v>24</v>
       </c>
       <c r="S2" t="s">
         <v>24</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="U2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" t="s">
+        <v>79</v>
+      </c>
+      <c r="W2" t="s">
+        <v>107</v>
+      </c>
+      <c r="X2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1086,9 +1220,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="216" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>9</v>

--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F47DA49-A83E-4E9C-863B-A8F920B5E83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840E90A2-8FE2-4A57-9E09-83514A9696FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -366,6 +363,9 @@
   </si>
   <si>
     <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: SIC Code is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Tail Expires is required.Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: \"Women Led\" is required. Please update this field with the correct valueInfo--&gt;Administration: Fairness Opinion Component is required.Info--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -721,24 +721,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -761,165 +761,165 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="L2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M2" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="N2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="R2" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD1" s="1" t="s">
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="U2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W2" t="s">
+        <v>106</v>
+      </c>
+      <c r="X2" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>90</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>104</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="R2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="U2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V2" t="s">
-        <v>79</v>
-      </c>
-      <c r="W2" t="s">
-        <v>107</v>
-      </c>
-      <c r="X2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>104</v>
-      </c>
       <c r="AD2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -931,23 +931,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -958,19 +958,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -981,16 +981,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1001,90 +1001,90 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="86.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="86.7109375" customWidth="1"/>
     <col min="10" max="10" width="45" customWidth="1"/>
-    <col min="11" max="11" width="54.44140625" customWidth="1"/>
+    <col min="11" max="11" width="54.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>27</v>
-      </c>
       <c r="C1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="H1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1096,319 +1096,319 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AF33"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="95.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="6" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="6"/>
-    <col min="8" max="8" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.88671875" style="6"/>
-    <col min="13" max="13" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="2"/>
-    <col min="15" max="16" width="8.88671875" style="6"/>
-    <col min="17" max="17" width="10.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.88671875" style="6"/>
-    <col min="21" max="21" width="9.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.88671875" style="6"/>
-    <col min="23" max="23" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.88671875" style="6"/>
-    <col min="31" max="31" width="10.5546875" style="6" customWidth="1"/>
-    <col min="32" max="32" width="102.33203125" style="6" customWidth="1"/>
-    <col min="33" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="95.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="6"/>
+    <col min="8" max="8" width="12.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.85546875" style="6"/>
+    <col min="13" max="13" width="10.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="2"/>
+    <col min="15" max="16" width="8.85546875" style="6"/>
+    <col min="17" max="17" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.85546875" style="6"/>
+    <col min="21" max="21" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.85546875" style="6"/>
+    <col min="23" max="23" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.85546875" style="6"/>
+    <col min="31" max="31" width="10.5703125" style="6" customWidth="1"/>
+    <col min="32" max="32" width="102.28515625" style="6" customWidth="1"/>
+    <col min="33" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="D1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="R1" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="S1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="T1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="225" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="U1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="W1" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF1" s="7" t="s">
+      <c r="S2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF2" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:32" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
     </row>
   </sheetData>

--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840E90A2-8FE2-4A57-9E09-83514A9696FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20129106-B7FD-4C87-94F5-A69201A6F440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>

--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20129106-B7FD-4C87-94F5-A69201A6F440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC17144-374F-4EF6-859C-17E9714CAE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -362,10 +362,10 @@
     <t>Consulting</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: SIC Code is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Tail Expires is required.Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: \"Women Led\" is required. Please update this field with the correct valueInfo--&gt;Administration: Fairness Opinion Component is required.Info--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
-  </si>
-  <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Tail Expires is required.Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Fairness Opinion Component is required.Info--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
   </si>
 </sst>
 </file>
@@ -841,7 +841,7 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="2" spans="1:32" ht="225" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>8</v>

--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC17144-374F-4EF6-859C-17E9714CAE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A907D23-6D1B-44AC-916C-CC0CA555E908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
   <si>
     <t>Client</t>
   </si>
@@ -41,9 +41,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -296,9 +293,6 @@
     <t>Dimitri Drone</t>
   </si>
   <si>
-    <t>Activism Advisory</t>
-  </si>
-  <si>
     <t>HL Capital, Inc.</t>
   </si>
   <si>
@@ -341,9 +335,6 @@
     <t>WomenLed</t>
   </si>
   <si>
-    <t>James Craven</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -356,16 +347,28 @@
     <t>Cleared</t>
   </si>
   <si>
-    <t>CF</t>
-  </si>
-  <si>
     <t>Consulting</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Fees &amp; Financials--&gt;Estimated Fees: Tail Expires is required.Fees &amp; Financials--&gt;Estimated Fees: Progress/Monthly Fee is required.Fees &amp; Financials--&gt;Estimated Fees: Contingent Fee is required.Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Estimated Close Date is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Fairness Opinion Component is required.Info--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.</t>
+    <t>FVA</t>
+  </si>
+  <si>
+    <t>CVAS - IP Valuation</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>No Restrictions</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
   </si>
 </sst>
 </file>
@@ -425,9 +428,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -440,6 +440,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,24 +724,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -749,177 +768,177 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="N1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="T1" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>88</v>
+    </row>
+    <row r="2" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="D2" t="s">
         <v>110</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>89</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
+      <c r="E2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="N2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="U2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="W2" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="X2" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="R2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="2" t="s">
+      <c r="Y2" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z2" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="U2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W2" t="s">
-        <v>106</v>
-      </c>
-      <c r="X2" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC2" t="s">
         <v>109</v>
       </c>
-      <c r="AA2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>103</v>
-      </c>
       <c r="AD2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -931,23 +950,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -958,19 +977,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -981,16 +1000,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1001,90 +1020,90 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="86.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="86.6640625" customWidth="1"/>
     <col min="10" max="10" width="45" customWidth="1"/>
-    <col min="11" max="11" width="54.42578125" customWidth="1"/>
+    <col min="11" max="11" width="54.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="H1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="E2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="7" t="s">
+      <c r="G2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="I2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1096,319 +1115,316 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AF33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="95.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="6"/>
-    <col min="8" max="8" width="12.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.85546875" style="6"/>
-    <col min="13" max="13" width="10.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="2"/>
-    <col min="15" max="16" width="8.85546875" style="6"/>
-    <col min="17" max="17" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.85546875" style="6"/>
-    <col min="21" max="21" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.85546875" style="6"/>
-    <col min="23" max="23" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.85546875" style="6"/>
-    <col min="31" max="31" width="10.5703125" style="6" customWidth="1"/>
-    <col min="32" max="32" width="102.28515625" style="6" customWidth="1"/>
-    <col min="33" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="95.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="5"/>
+    <col min="8" max="8" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.88671875" style="5"/>
+    <col min="13" max="13" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="2"/>
+    <col min="15" max="16" width="8.88671875" style="5"/>
+    <col min="17" max="17" width="10.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.88671875" style="5"/>
+    <col min="21" max="21" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="5"/>
+    <col min="23" max="23" width="13.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.88671875" style="5"/>
+    <col min="31" max="31" width="10.5546875" style="5" customWidth="1"/>
+    <col min="32" max="32" width="102.33203125" style="5" customWidth="1"/>
+    <col min="33" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" s="7" t="s">
+      <c r="D2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="U1" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="W1" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y1" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF1" s="7" t="s">
+      <c r="S2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF2" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="225" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:32" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
     </row>
   </sheetData>

--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A907D23-6D1B-44AC-916C-CC0CA555E908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA88346-FC46-4A57-893E-2CDDCACC5569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -362,13 +362,13 @@
     <t>No Restrictions</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
-  </si>
-  <si>
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
     <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
+  </si>
+  <si>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -724,40 +724,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -768,7 +768,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -849,7 +849,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>76</v>
       </c>
@@ -860,7 +860,7 @@
         <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>6</v>
@@ -950,13 +950,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -964,7 +964,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -977,17 +977,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -1000,14 +1000,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1020,20 +1020,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="86.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="86.7109375" customWidth="1"/>
     <col min="10" max="10" width="45" customWidth="1"/>
-    <col min="11" max="11" width="54.44140625" customWidth="1"/>
+    <col min="11" max="11" width="54.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>77</v>
       </c>
@@ -1115,33 +1115,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AF33"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="95.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="5"/>
-    <col min="8" max="8" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.88671875" style="5"/>
-    <col min="13" max="13" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="2"/>
-    <col min="15" max="16" width="8.88671875" style="5"/>
-    <col min="17" max="17" width="10.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.88671875" style="5"/>
-    <col min="21" max="21" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.88671875" style="5"/>
-    <col min="23" max="23" width="13.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.88671875" style="5"/>
-    <col min="31" max="31" width="10.5546875" style="5" customWidth="1"/>
-    <col min="32" max="32" width="102.33203125" style="5" customWidth="1"/>
-    <col min="33" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="95.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="5"/>
+    <col min="8" max="8" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.85546875" style="5"/>
+    <col min="13" max="13" width="10.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="2"/>
+    <col min="15" max="16" width="8.85546875" style="5"/>
+    <col min="17" max="17" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.85546875" style="5"/>
+    <col min="21" max="21" width="9.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.85546875" style="5"/>
+    <col min="23" max="23" width="13.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.85546875" style="5"/>
+    <col min="31" max="31" width="10.5703125" style="5" customWidth="1"/>
+    <col min="32" max="32" width="102.28515625" style="5" customWidth="1"/>
+    <col min="33" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>38</v>
       </c>
@@ -1239,9 +1239,9 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" ht="195" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>7</v>
@@ -1337,94 +1337,94 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:32" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
     </row>
   </sheetData>

--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F9B58F-12AD-41FF-826F-4A29F56E4878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D71BCE-5F82-43E5-9001-E94584E367D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -365,10 +365,10 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
-  </si>
-  <si>
     <t>BUS - Business Services</t>
+  </si>
+  <si>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Service Benefit was provided is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
   </si>
 </sst>
 </file>
@@ -860,7 +860,7 @@
         <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>6</v>
@@ -1239,9 +1239,9 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="195" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" ht="210" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>7</v>

--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D71BCE-5F82-43E5-9001-E94584E367D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93444EA3-5E78-450D-A3EA-71BFA23F2452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -368,7 +368,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Service Benefit was provided is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
   </si>
 </sst>
 </file>
@@ -724,40 +724,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -849,7 +849,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>76</v>
       </c>
@@ -950,13 +950,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -964,7 +964,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -977,17 +977,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -1000,14 +1000,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1020,20 +1020,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="86.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="86.6640625" customWidth="1"/>
     <col min="10" max="10" width="45" customWidth="1"/>
-    <col min="11" max="11" width="54.42578125" customWidth="1"/>
+    <col min="11" max="11" width="54.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>77</v>
       </c>
@@ -1115,33 +1115,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AF33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="95.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="5"/>
-    <col min="8" max="8" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.85546875" style="5"/>
-    <col min="13" max="13" width="10.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="2"/>
-    <col min="15" max="16" width="8.85546875" style="5"/>
-    <col min="17" max="17" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.85546875" style="5"/>
-    <col min="21" max="21" width="9.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.85546875" style="5"/>
-    <col min="23" max="23" width="13.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.85546875" style="5"/>
-    <col min="31" max="31" width="10.5703125" style="5" customWidth="1"/>
-    <col min="32" max="32" width="102.28515625" style="5" customWidth="1"/>
-    <col min="33" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="95.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="5"/>
+    <col min="8" max="8" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.88671875" style="5"/>
+    <col min="13" max="13" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="2"/>
+    <col min="15" max="16" width="8.88671875" style="5"/>
+    <col min="17" max="17" width="10.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.88671875" style="5"/>
+    <col min="21" max="21" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="5"/>
+    <col min="23" max="23" width="13.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.88671875" style="5"/>
+    <col min="31" max="31" width="10.5546875" style="5" customWidth="1"/>
+    <col min="32" max="32" width="102.33203125" style="5" customWidth="1"/>
+    <col min="33" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>38</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="210" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>112</v>
       </c>
@@ -1337,94 +1337,94 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:32" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
     </row>
   </sheetData>

--- a/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
+++ b/TestData/LV_T1692_ValidationsToBeCompletedBeforeFVAOpportunityIsApproved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93444EA3-5E78-450D-A3EA-71BFA23F2452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2AE4EF-062A-42BB-96DD-758D28EA458C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -368,7 +368,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)Client/Subject &amp; Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
+    <t>Items to complete:Info--&gt;Details--&gt;General: Client Ownership is required.Info--&gt;Details--&gt;General: Subject's Ownership is required.Info--&gt;Details--&gt;General: Tombstone Permission is required.Info--&gt;Details--&gt;Opportunity Description: Opportunity Description is required.Fees &amp; Financials--&gt;Funds &amp; Financials: Est. Transaction Size / Market Cap (MM) is required.Fees &amp; Financials--&gt;Estimated Fees: Retainer is required. (Input zero if there's no Retainer fee.)KYC/Client/Subject/Referral--&gt;Referral Info: Referral Contact is required.Internal Team: Team must include the following roles: Initiator, Seller, Principal, Manager, Associate(Optional), Analyst(Optional).Compliance &amp; Legal--&gt;Legal Matters: Confidentiality Agreement is required.Compliance &amp; Legal--&gt;Conflicts Check: A Conflicts Check was completed more than 30 days ago. A new Conflicts Check must be completed.Info--&gt;Administration: Location where Benefit is to be Provided is required.Info--&gt;Administration: "Women Led" is required. Please update this field with the correct valueInfo--&gt;Administration: Date Engaged - Date of Executed Retainer or similar document.Opportunity Contacts - Add at least one Primary Opportunity Contact.Opportunity Contacts - Add at least one Billing Contact.Fees &amp; Financials--&gt;Estimated Fees: Total Anticipated Revenue is required.It should be Greater Than or Equal to the Fee.</t>
   </si>
 </sst>
 </file>
@@ -724,40 +724,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -849,7 +849,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>76</v>
       </c>
@@ -950,13 +950,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -964,7 +964,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -977,17 +977,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8244481F-F1B5-4BC7-BE8A-260AA0DF5D37}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -1000,14 +1000,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB45B32-4FF3-421E-8C03-B189CD186655}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1020,20 +1020,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="86.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="86.7109375" customWidth="1"/>
     <col min="10" max="10" width="45" customWidth="1"/>
-    <col min="11" max="11" width="54.44140625" customWidth="1"/>
+    <col min="11" max="11" width="54.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>77</v>
       </c>
@@ -1115,33 +1115,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AF33"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="95.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="5"/>
-    <col min="8" max="8" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.88671875" style="5"/>
-    <col min="13" max="13" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="2"/>
-    <col min="15" max="16" width="8.88671875" style="5"/>
-    <col min="17" max="17" width="10.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.88671875" style="5"/>
-    <col min="21" max="21" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.88671875" style="5"/>
-    <col min="23" max="23" width="13.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.88671875" style="5"/>
-    <col min="31" max="31" width="10.5546875" style="5" customWidth="1"/>
-    <col min="32" max="32" width="102.33203125" style="5" customWidth="1"/>
-    <col min="33" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="95.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="5"/>
+    <col min="8" max="8" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.85546875" style="5"/>
+    <col min="13" max="13" width="10.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="2"/>
+    <col min="15" max="16" width="8.85546875" style="5"/>
+    <col min="17" max="17" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.85546875" style="5"/>
+    <col min="21" max="21" width="9.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.85546875" style="5"/>
+    <col min="23" max="23" width="13.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.85546875" style="5"/>
+    <col min="31" max="31" width="10.5703125" style="5" customWidth="1"/>
+    <col min="32" max="32" width="102.28515625" style="5" customWidth="1"/>
+    <col min="33" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>38</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" ht="210" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>112</v>
       </c>
@@ -1337,94 +1337,94 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:32" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
     </row>
   </sheetData>
